--- a/光伏配储项目/电价数据/2026/金山站.xlsx
+++ b/光伏配储项目/电价数据/2026/金山站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5099</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.72472</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56502</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5199400000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.45574</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43784</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45466</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4089100000000001</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41287</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41423</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42422</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41305</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44424</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26854</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.21803</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.26079</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07873000000000001</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06455</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.05368</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.03454</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.05577</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.0391</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04658</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.01264</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.01177</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08633</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.01842</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.00115</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00366</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14529</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21304</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23621</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.21623</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.11955</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.00068</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00661</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.16161</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.19418</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.19494</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22528</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.25798</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.12557</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.19811</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.27662</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.01099</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.24652</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.03211</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.45807</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.48896</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.52865</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.48702</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.7669900000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.61563</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.5154099999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.51811</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.15384</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.5917899999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.54457</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.28179</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.50346</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.50612</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.61878</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.57516</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43495</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.5080899999999999</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.45615</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.47007</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.62621</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.43379</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.75815</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.17053</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.85765</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.54627</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52785</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50773</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5166499999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.5118199999999999</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39529</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47746</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37475</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37246</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37739</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42552</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.52896</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6562899999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7538400000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44308</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.42257</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.09076999999999999</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.04301</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.26511</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.27085</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30598</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.26331</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.59346</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.24092</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.27839</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.27593</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.5872999999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.26848</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.23347</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.23581</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.26368</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.2719</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.27398</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.44182</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.42529</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.27381</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.48235</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.71047</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.9165099999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.8787999999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.84949</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.4458</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.8325900000000001</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.29357</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43846</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.59901</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4391600000000001</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43387</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4079700000000001</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.39316</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.34341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.53854</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.47419</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36518</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.41302</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.41071</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.42079</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.39505</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.3935</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.37951</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44852</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40646</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.28562</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.16977</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.38814</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.43906</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.48605</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.45563</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.27426</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.21914</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.15172</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.20954</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.19659</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24905</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27978</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.25332</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.22382</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.28549</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.48277</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5036700000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.29308</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34414</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.26925</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.27291</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47939</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.27291</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.28077</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.28267</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.27938</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.28001</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.29961</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.29828</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.27858</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.26095</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26399</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.19477</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.10839</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11291</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08209999999999999</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.24978</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.21147</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.13381</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28876</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.21654</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.04103</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.04207</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06114</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.27164</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.1753</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.00551</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.21262</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.00068</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.03247999999999999</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.04991</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.07795999999999999</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.29203</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.19954</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.16496</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.20236</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.15011</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.19413</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14131</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.1982</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.22618</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.27865</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.2584</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28826</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.46928</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.29946</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30118</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.29233</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.25446</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29233</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28997</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29223</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30022</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.29812</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.27511</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.2734</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.27612</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30124</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26046</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04076</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04513</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04028</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04002</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04267</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04497</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04347</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04549</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04661</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04714</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04801</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04651</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04686</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04769</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04692</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04593999999999999</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04808</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04654</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04806000000000001</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04926</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04884</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04652000000000001</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04732</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22001</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.0464</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04878</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05158</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14712</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03761</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09888</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39537</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41729</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35132</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6644600000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44655</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42373</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10244</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04264</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04588</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04506</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04397</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03237</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04064</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10696</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00111</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.0374</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04686999999999999</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04104</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04121</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04113</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04365</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04352</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04102</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04043</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04324</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04028</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03892</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04103</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04212</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.03995</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04263</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04301</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04641</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04598</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2024</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14485</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29761</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27145</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3378</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32304</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40743</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.2906</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28385</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27357</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27373</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28344</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17441</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.16067</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1733</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14963</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16135</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.16074</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23968</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21616</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22877</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27205</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28862</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29319</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28385</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28348</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27094</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28325</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.39828</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.42143</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.47122</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.5786399999999999</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.45863</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.45407</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39066</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.42961</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15728</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.40946</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50751</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79108</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6219199999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78086</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92003</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4943</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92831</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.90759</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31989</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.39724</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.9307300000000001</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6389400000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.22957</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88983</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.58143</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.37441</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.06282</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.57448</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8281000000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53076</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.81031</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.80713</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.88136</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.89336</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.52801</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.43272</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.44465</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.48974</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.25176</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.88009</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55179</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.66626</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54938</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.51047</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46126</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.4295</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45206</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39941</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45327</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42243</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39701</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41534</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43439</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.37423</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41393</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45134</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58974</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42855</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59687</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60202</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.64425</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45491</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.44395</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.6451399999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44744</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8652300000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.7839400000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.9017999999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.8859600000000001</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8865499999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43433</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.42521</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.47686</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27343</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41029</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45282</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35328</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.02728</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.50019</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.50448</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.62421</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.69896</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4099</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.45167</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.5142</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50063</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30395</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28913</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16474</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28533</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2611</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20122</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27747</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.45254</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27599</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29051</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.24819</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27492</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42798</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44697</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42071</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40075</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59766</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8897699999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.3579</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13635</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.71204</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.80614</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65123</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.59108</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45033</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50042</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43988</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42367</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5008899999999999</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41317</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42832</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45074</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43441</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41289</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42384</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39602</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.75493</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.40373</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.39671</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.16067</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.6562100000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24997</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.02267</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.90813</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.23908</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.58125</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.7712100000000001</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.27095</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.48324</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.48929</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.43281</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36518</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.60881</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46579</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.68291</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46677</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43965</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42567</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38822</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32658</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42579</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.12304</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23728</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.1466</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14931</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15626</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14482</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14243</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14489</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14383</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25904</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14552</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26879</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14342</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05404</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11483</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11376</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14771</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14786</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28883</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45145</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39367</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40369</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43765</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44185</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4413</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44625</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.4455</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40431</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39908</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39279</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35073</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.58497</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47038</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42547</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41748</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38211</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39468</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.5435</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.40973</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.41038</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.39397</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.22968</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.42693</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.42575</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.42301</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44835</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.46155</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.2497</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.42772</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.51613</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36065</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36664</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42046</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39235</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.43459</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.46099</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.45261</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.29187</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.27043</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37267</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03244</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25518</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.2116</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07547</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18518</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24511</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28664</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.27172</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25378</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27529</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29783</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.50808</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41741</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.78071</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.45376</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47131</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.44068</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41785</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31068</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.43016</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28268</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39612</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38561</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.35233</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.42741</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.7435</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.41715</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42953</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40727</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39201</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64951</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.87909</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48802</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.4605</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34508</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26154</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13651</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28273</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19538</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24664</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.03005</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.13126</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.02099</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23802</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28745</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24838</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.00435</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14518</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.01927</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.23559</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.23808</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.29829</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41792</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40918</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6373300000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60634</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5839</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46228</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.58633</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47845</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.74061</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45448</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46026</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40235</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48197</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43062</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41999</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3602</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49356</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.47607</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4674700000000001</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.45848</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42162</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40756</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41405</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41145</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41986</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40198</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41409</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41906</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45083</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45004</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5614</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50097</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45099</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.41849</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42008</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42725</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.37317</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.40788</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.4079100000000001</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40863</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43477</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.39316</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.04406</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.03687</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.46328</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.84934</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.16454</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.10915</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.01212</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.27083</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.03913000000000001</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41603</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48626</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.45088</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50847</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.42989</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.58161</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.66806</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.65398</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.62863</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.6913400000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.51375</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.50083</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.7599</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.70378</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.57368</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6165499999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.40659</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.46641</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.46287</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.45628</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.51266</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41644</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.43314</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.44667</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42811</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41905</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44378</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41134</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44768</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39518</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40227</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38647</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38866</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39476</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.28034</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.27486</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.0394</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40835</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37214</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45269</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40738</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46368</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01475</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18509</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.39861</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39413</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36267</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44383</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.44378</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.46027</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24986</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23566</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29845</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23739</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24695</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25221</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.04148</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.17247</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.05903</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.17684</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25962</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.04208</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14882</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.1524</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.0604</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.01217</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.25411</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25678</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28366</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.38955</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.43275</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.5324099999999999</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37218</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35405</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.19117</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.18375</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.13031</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.14865</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.04973</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01621</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00145</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.04368</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04143</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.01419</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.07074</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.13753</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.18997</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27698</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.22232</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.22292</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.22379</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.22802</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.23822</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.26522</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.24791</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.24108</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.23243</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.24821</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25185</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.23462</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.25312</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.24178</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.25924</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.24707</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.26008</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.25734</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.21628</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.23704</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.21464</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.18365</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.08017000000000001</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.04252</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.23101</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.1516</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.15202</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.15243</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.01817</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.23191</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.21425</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.19941</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16243</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15464</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.12981</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.15393</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.18676</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.10672</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.12044</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.18963</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.15742</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.20908</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.18094</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.16876</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.21938</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.16799</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.21926</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.22642</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.20867</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.21557</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.12858</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.43971</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.18924</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>-0.00254</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.16938</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.16597</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.00651</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.02758</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.18604</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.26519</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.03238000000000001</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.07901000000000001</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.01003</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23552</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25336</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.28302</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30665</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.20512</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32632</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.10562</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.27975</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.42206</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.26314</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25628</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.12293</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24598</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.30821</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39804</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.44905</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30197</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.17113</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25725</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26984</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.19051</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14334</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.10723</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.38873</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3322</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.23981</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.26276</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37424</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.27823</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.61341</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.42624</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.6077100000000001</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.25904</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.29699</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.27507</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28445</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.28302</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.2685</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.1794</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.26239</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.26505</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.26789</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26362</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35728</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.24919</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.2835299999999999</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.28284</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.41087</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.41177</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.47293</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.4828</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.58131</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.6019500000000001</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.6009500000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.52504</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41275</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.09206</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.39278</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.43007</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.46536</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40619</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.55104</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.48009</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.39031</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.45739</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.43149</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.8882100000000001</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.50188</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.42944</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40305</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39077</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36904</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46799</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37951</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.37214</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.3728399999999999</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.29851</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.46772</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.21194</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.17891</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.2358</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.26293</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.19432</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.26791</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.27849</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.46364</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36858</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41561</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39547</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39254</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46695</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.56086</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5611900000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46241</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.55222</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46589</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.38154</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49853</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.53347</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.5211399999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.71321</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7585499999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.55088</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5535599999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44503</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37692</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27244</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30362</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.29019</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.2706</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.26722</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.27876</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.2661</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.2618</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.25417</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.24731</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.23755</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.23628</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.25334</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.18951</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.21148</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.13642</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.00203</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.03576</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.16641</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01332</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.13354</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.00495</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.01378</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01075</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.0227</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.02185</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23557</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.01442</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03126</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02214</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.01642</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.0186</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.02968</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.10424</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.06529</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11902</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.13903</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.22279</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18114</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.1879</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.29764</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.20724</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.24906</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36874</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40538</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39304</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37198</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41949</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38088</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.7386200000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.28321</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.2752</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.26093</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.23223</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22609</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.19517</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.19514</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.19959</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.21496</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.10922</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01672</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03609</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.05299</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00483</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01414</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04418</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.02257</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.02826</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15518</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.22322</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04808</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.18552</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.18076</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.13441</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.19414</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.16164</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.18897</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.22708</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.1807</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.23151</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.29519</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.26956</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43296</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39362</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5283300000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38997</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.3838</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39794</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40874</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43156</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.38607</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38686</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.51218</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41711</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.27059</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.23061</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.18491</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.17033</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.11169</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.14636</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.17254</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.15969</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.08592</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.10281</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04775</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.06872</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03684</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03761</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03834000000000001</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03719</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04508</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05086</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.05933</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03418</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.05612</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.07081999999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.11292</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.13874</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.08538</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.16075</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.14237</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.08802</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04593999999999999</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21343</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.09398999999999999</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.18553</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.12834</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.13953</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.16409</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.14455</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.17916</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.19796</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.19902</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.21176</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.25404</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.25792</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.25943</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.28131</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40468</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.27207</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37747</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.41365</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42079</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4982200000000001</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.41047</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44383</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41541</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39768</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41496</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38208</v>
       </c>
     </row>
   </sheetData>
